--- a/docs/Indefinido_full_irreg_50_DEF.xlsx
+++ b/docs/Indefinido_full_irreg_50_DEF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iese365-my.sharepoint.com/personal/cschmidtf_iese_edu/Documents/Carlos S/Ak uni/AkaApp/Revisados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rogergongas/Developer/BSP/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{98314AD1-930B-4FA1-95D2-81626898E457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81CE52CB-C209-4D9E-A297-0E59086F8219}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9A3907-9B09-7F43-9FC5-7E6709A8EE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3204" yWindow="3204" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3100" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All_Items" sheetId="1" r:id="rId1"/>
@@ -267,9 +267,6 @@
     <t>Al final del viaje, le (Nosotros) ___ las gracias al guía, y también una buena propina.</t>
   </si>
   <si>
-    <t>Hace unos días, fuimos a Girona. ___ una vuelta por el centro y comimos en un buen restaurante.</t>
-  </si>
-  <si>
     <t>disteis</t>
   </si>
   <si>
@@ -439,6 +436,9 @@
   </si>
   <si>
     <t>Infinitivos</t>
+  </si>
+  <si>
+    <t>Cuando fuisteis a Girona, ¿(Vosotros) ___ una vuelta por el centro?</t>
   </si>
 </sst>
 </file>
@@ -729,16 +729,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="92.375" customWidth="1"/>
+    <col min="2" max="2" width="92.33203125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:5" ht="16.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1579,10 +1579,10 @@
         <v>61</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>64</v>
@@ -1596,10 +1596,10 @@
         <v>61</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>64</v>
@@ -1619,7 +1619,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="76" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1627,9 +1627,9 @@
     <col min="4" max="4" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:4" ht="16.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>14</v>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>14</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>14</v>
@@ -1741,7 +1741,7 @@
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>19</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>30</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>30</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>36</v>
@@ -1895,7 +1895,7 @@
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>36</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>36</v>
@@ -1932,7 +1932,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="76" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1940,9 +1940,9 @@
     <col min="4" max="4" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:4" ht="16.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>14</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>14</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>14</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>19</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>30</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>30</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>36</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>36</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>36</v>
@@ -2245,7 +2245,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="76" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2253,9 +2253,9 @@
     <col min="4" max="4" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:4" ht="16.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>63</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>63</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>67</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>67</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>70</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>70</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>73</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>73</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>64</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>64</v>
@@ -2418,7 +2418,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
   </cols>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2457,7 +2457,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5">
         <v>50</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
